--- a/week-01/Ex5B_Resturantcustomersurveyresults.xlsx
+++ b/week-01/Ex5B_Resturantcustomersurveyresults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/locelotllopez_my_yearupunited_org/Documents/data analytics/week-01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{AA70DF7C-8EBA-49B5-B14A-A4CF8BF79873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="14_{AA70DF7C-8EBA-49B5-B14A-A4CF8BF79873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F558F77-D81F-44DB-8354-8BBA5AB015E0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="count recommend" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="52">
   <si>
     <t>Id</t>
   </si>
@@ -216,6 +216,9 @@
   <si>
     <t>Sum of Staff Quality? 1-bad, 5-Great</t>
   </si>
+  <si>
+    <t>Sum of Quality of food? 1-bad 5- great</t>
+  </si>
 </sst>
 </file>
 
@@ -253,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -262,13 +265,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -276,21 +282,16 @@
   </cellStyles>
   <dxfs count="26">
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -302,13 +303,21 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -329,22 +338,19 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="28" formatCode="mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="28" formatCode="mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
@@ -1156,6 +1162,90 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="8"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
         <c:spPr>
           <a:gradFill rotWithShape="1">
             <a:gsLst>
@@ -2218,8 +2308,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2268,21 +2357,21 @@
           <a:gradFill rotWithShape="1">
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="accent6">
+                <a:schemeClr val="accent2">
                   <a:satMod val="103000"/>
                   <a:lumMod val="102000"/>
                   <a:tint val="94000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="50000">
-                <a:schemeClr val="accent6">
+                <a:schemeClr val="accent2">
                   <a:satMod val="110000"/>
                   <a:lumMod val="100000"/>
                   <a:shade val="100000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="100000">
-                <a:schemeClr val="accent6">
+                <a:schemeClr val="accent2">
                   <a:lumMod val="99000"/>
                   <a:satMod val="120000"/>
                   <a:shade val="78000"/>
@@ -2302,46 +2391,6 @@
             </a:outerShdw>
           </a:effectLst>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="2"/>
@@ -2360,46 +2409,6 @@
             </a:outerShdw>
           </a:effectLst>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="3"/>
@@ -2407,21 +2416,21 @@
           <a:gradFill rotWithShape="1">
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="accent4">
+                <a:schemeClr val="accent2">
                   <a:satMod val="103000"/>
                   <a:lumMod val="102000"/>
                   <a:tint val="94000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="50000">
-                <a:schemeClr val="accent4">
+                <a:schemeClr val="accent2">
                   <a:satMod val="110000"/>
                   <a:lumMod val="100000"/>
                   <a:shade val="100000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="100000">
-                <a:schemeClr val="accent4">
+                <a:schemeClr val="accent2">
                   <a:lumMod val="99000"/>
                   <a:satMod val="120000"/>
                   <a:shade val="78000"/>
@@ -2441,46 +2450,6 @@
             </a:outerShdw>
           </a:effectLst>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -2834,6 +2803,609 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Ex5B_Resturantcustomersurveyresults.xlsx]count recommend!PivotTable3</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Food Quality Drives Recommendations</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.27642787243189426"/>
+          <c:y val="8.2385535141440668E-3"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11085774165082812"/>
+          <c:y val="0.16143299795858848"/>
+          <c:w val="0.78645603674540687"/>
+          <c:h val="0.53774387576552929"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'count recommend'!$B$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'count recommend'!$A$27:$A$34</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="4"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>5</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>NEVER</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>NOT SURE</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>VERY LIKELY</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'count recommend'!$B$27:$B$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E7D4-4962-91A4-486C2F3A2407}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="844773903"/>
+        <c:axId val="844771983"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="844773903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="844771983"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="844771983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="844773903"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.91923505520861615"/>
+          <c:y val="0.35641185476815396"/>
+          <c:w val="6.4487595031224546E-2"/>
+          <c:h val="8.1597769028871406E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2911,6 +3483,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
   <cs:axisTitle>
@@ -3898,6 +4510,502 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -3977,6 +5085,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{981E13C9-CFA3-EC20-3F65-81AF165A02D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4008,7 +5152,11 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Quality of food? 1-bad 5- great" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5" count="3">
+        <n v="5"/>
+        <n v="1"/>
+        <n v="4"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Staff Quality? 1-bad, 5-Great" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5" count="3">
@@ -4067,7 +5215,7 @@
     <s v="locelotllopez@my.yearupunited.org"/>
     <s v="luis ocelotllopez"/>
     <m/>
-    <n v="5"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <s v="Weekly"/>
@@ -4084,7 +5232,7 @@
     <s v="anonymous"/>
     <m/>
     <s v="John pizza"/>
-    <n v="1"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Every other month"/>
@@ -4101,7 +5249,7 @@
     <s v="anonymous"/>
     <m/>
     <s v="girt"/>
-    <n v="1"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="1"/>
     <s v="Every other month"/>
@@ -4118,7 +5266,7 @@
     <s v="anonymous"/>
     <m/>
     <s v="Alexus"/>
-    <n v="4"/>
+    <x v="2"/>
     <x v="2"/>
     <x v="0"/>
     <s v="Weekly"/>
@@ -4135,7 +5283,7 @@
     <s v="anonymous"/>
     <m/>
     <s v="Charles"/>
-    <n v="5"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="2"/>
     <s v="Monthly"/>
@@ -4152,7 +5300,7 @@
     <s v="anonymous"/>
     <m/>
     <s v="luis"/>
-    <n v="5"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="2"/>
     <s v="Every other month"/>
@@ -4169,7 +5317,7 @@
     <s v="anonymous"/>
     <m/>
     <s v="Bess"/>
-    <n v="5"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="2"/>
     <s v="Monthly"/>
@@ -4186,7 +5334,7 @@
     <s v="anonymous"/>
     <m/>
     <s v="Smaya "/>
-    <n v="5"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="2"/>
     <s v="Weekly"/>
@@ -4203,7 +5351,7 @@
     <s v="anonymous"/>
     <m/>
     <s v="Tihitina"/>
-    <n v="4"/>
+    <x v="2"/>
     <x v="0"/>
     <x v="2"/>
     <s v="Weekly"/>
@@ -4220,7 +5368,7 @@
     <s v="anonymous"/>
     <m/>
     <s v="Sonia "/>
-    <n v="5"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="2"/>
     <s v="Weekly"/>
@@ -4233,7 +5381,107 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{32E3FF99-E1F9-468C-A1AF-636BBE26DE93}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A5169734-63F1-41A7-833A-CF16C67A1899}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="A26:B34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="45" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="9"/>
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Quality of food? 1-bad 5- great" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{32E3FF99-E1F9-468C-A1AF-636BBE26DE93}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16">
   <location ref="J10:K14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -4341,8 +5589,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B3DC7A73-F288-4CB4-B59D-EA9F9B139718}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B3DC7A73-F288-4CB4-B59D-EA9F9B139718}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:I8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -4429,7 +5677,7 @@
   <dataFields count="1">
     <dataField name="Count of Would you recommend us to a family or friend?" fld="9" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="8">
+  <chartFormats count="9">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -4523,6 +5771,18 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="0" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="11" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -4547,46 +5807,46 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="24" totalsRowDxfId="10">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="24" totalsRowDxfId="23">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="startDate"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="23" totalsRowDxfId="9">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="22" totalsRowDxfId="21">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="submitDate"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{6B54B6E7-A4E6-49DA-818D-0CAE7F435F26}" name="Time to Complete" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="8">
+    <tableColumn id="15" xr3:uid="{6B54B6E7-A4E6-49DA-818D-0CAE7F435F26}" name="Time to Complete" totalsRowFunction="custom" dataDxfId="20" totalsRowDxfId="19">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(D2:D11)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="21" totalsRowDxfId="7">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="18" totalsRowDxfId="17">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="20" totalsRowDxfId="6">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="16" totalsRowDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="First name." dataDxfId="19" totalsRowDxfId="5">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="First name." dataDxfId="14" totalsRowDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rdf80a9f0298d453c865f40badb78c0cc"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Quality of food? 1-bad 5- great" totalsRowFunction="custom" dataDxfId="18">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Quality of food? 1-bad 5- great" totalsRowFunction="custom" dataDxfId="12">
       <totalsRowFormula>AVERAGE(H2:H11)</totalsRowFormula>
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
@@ -4594,7 +5854,7 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Staff Quality? 1-bad, 5-Great" totalsRowFunction="custom" dataDxfId="17">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Staff Quality? 1-bad, 5-Great" totalsRowFunction="custom" dataDxfId="11">
       <totalsRowFormula>AVERAGE(I2:I11)</totalsRowFormula>
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
@@ -4602,14 +5862,14 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Would you recommend us to a family or friend?" dataDxfId="16" totalsRowDxfId="4">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Would you recommend us to a family or friend?" dataDxfId="10" totalsRowDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r81c8ae23a64b478c92d92167def60473"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Do you come in weekly, monthly or every other month?" totalsRowFunction="custom" dataDxfId="15" totalsRowDxfId="3">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Do you come in weekly, monthly or every other month?" totalsRowFunction="custom" dataDxfId="8" totalsRowDxfId="7">
       <totalsRowFormula>SUM(COUNTIF(OfficeForms.Table[Do you come in weekly, monthly or every other month?],"Monthly"), COUNTIF(OfficeForms.Table[Do you come in weekly, monthly or every other month?],"Every other month"))</totalsRowFormula>
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
@@ -4617,28 +5877,28 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="How do you Pay?" dataDxfId="14" totalsRowDxfId="2">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="How do you Pay?" dataDxfId="6" totalsRowDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rd273d3bf75a34e40ab84283088d017ce"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Preference in gaining rewards?" dataDxfId="13" totalsRowDxfId="1">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Preference in gaining rewards?" dataDxfId="4" totalsRowDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r66dc58864481414d9218fbf69f732f5c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Do you prefer rewards on your phone or gift card?" dataDxfId="12" totalsRowDxfId="0">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Do you prefer rewards on your phone or gift card?" dataDxfId="2" totalsRowDxfId="1">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r430b2e78e5764e4f9e9fd56c0b1ca763"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Would implementing rewards to your every day visit to Mario pizza, would you recommend us to a family or friends?" totalsRowFunction="custom" dataDxfId="11">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Would implementing rewards to your every day visit to Mario pizza, would you recommend us to a family or friends?" totalsRowFunction="custom" dataDxfId="0">
       <totalsRowFormula>AVERAGE(O2:O11)</totalsRowFormula>
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
@@ -4968,12 +6228,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484230C2-5233-4C1A-8F34-1BB676414222}">
-  <dimension ref="A3:K14"/>
+  <dimension ref="A3:K34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="49.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
@@ -4985,15 +6245,15 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B4" t="s">
@@ -5022,95 +6282,81 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6">
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6">
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6">
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6">
+      <c r="I6">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6">
+      <c r="H7">
         <v>2</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8">
         <v>2</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="7" t="s">
         <v>46</v>
       </c>
       <c r="K10" t="s">
@@ -5118,40 +6364,112 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>1</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="J12" s="9">
+      <c r="J12" s="8">
         <v>3</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <v>5</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13">
         <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="10">
+        <v>1</v>
+      </c>
+      <c r="B28" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="10">
+        <v>3</v>
+      </c>
+      <c r="B30" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="10">
+        <v>5</v>
+      </c>
+      <c r="B31" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="10">
+        <v>5</v>
+      </c>
+      <c r="B33" s="9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="9">
         <v>40</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -5672,12 +6990,11 @@
         <v>4</v>
       </c>
       <c r="J12" s="5"/>
-      <c r="K12" s="7">
+      <c r="K12" s="6">
         <f>SUM(COUNTIF(OfficeForms.Table[Do you come in weekly, monthly or every other month?],"Monthly"), COUNTIF(OfficeForms.Table[Do you come in weekly, monthly or every other month?],"Every other month"))</f>
         <v>5</v>
       </c>
       <c r="L12" s="2"/>
-      <c r="M12" s="6"/>
       <c r="N12" s="2"/>
       <c r="O12">
         <f>AVERAGE(O2:O11)</f>
